--- a/Data/Rules/Phillips Rules Matrix.xlsx
+++ b/Data/Rules/Phillips Rules Matrix.xlsx
@@ -4977,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="AO33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:41">
